--- a/docs/content_history/pbr-2025-vm20-table-j-swaps.xlsx
+++ b/docs/content_history/pbr-2025-vm20-table-j-swaps.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\PBR\VM20_VM22_ProductSupport\PBR Production Web Data\Current Year\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48FD5F4-752D-41D5-87B6-3A1CF4499AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BC708C-47D0-4A59-B2F9-89C12D28FB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2460" yWindow="2625" windowWidth="23460" windowHeight="12495" tabRatio="795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" tabRatio="795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="June_2025" sheetId="22" r:id="rId1"/>
-    <sheet name="May_2025" sheetId="21" r:id="rId2"/>
-    <sheet name="April_2025" sheetId="20" r:id="rId3"/>
-    <sheet name="March_2025" sheetId="19" r:id="rId4"/>
-    <sheet name="February_2025" sheetId="18" r:id="rId5"/>
-    <sheet name="January_2025" sheetId="17" r:id="rId6"/>
-    <sheet name="LIBOR to SOFR Disclosure" sheetId="16" r:id="rId7"/>
-    <sheet name="LEGAL DISCLAIMER" sheetId="11" r:id="rId8"/>
+    <sheet name="July_2025" sheetId="23" r:id="rId1"/>
+    <sheet name="June_2025" sheetId="22" r:id="rId2"/>
+    <sheet name="May_2025" sheetId="21" r:id="rId3"/>
+    <sheet name="April_2025" sheetId="20" r:id="rId4"/>
+    <sheet name="March_2025" sheetId="19" r:id="rId5"/>
+    <sheet name="February_2025" sheetId="18" r:id="rId6"/>
+    <sheet name="January_2025" sheetId="17" r:id="rId7"/>
+    <sheet name="LIBOR to SOFR Disclosure" sheetId="16" r:id="rId8"/>
+    <sheet name="LEGAL DISCLAIMER" sheetId="11" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="17">
   <si>
     <t>Table J (01/31/2025) Swap Benchmark Spreads (in bps)</t>
   </si>
@@ -85,6 +86,9 @@
   </si>
   <si>
     <t>Table J (06/30/2025) Swap Benchmark Spreads (in bps)</t>
+  </si>
+  <si>
+    <t>Table J (07/31/2025) Swap Benchmark Spreads (in bps)</t>
   </si>
 </sst>
 </file>
@@ -1314,7 +1318,7 @@
                   <a14:compatExt spid="_x0000_s4104"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000008100000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000008100000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1635,21 +1639,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE138FB-FABF-4565-91D3-7A1FC3DB0D62}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6CB6296-F480-49B2-B4EA-61908574360C}">
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="19.7109375" customWidth="1"/>
+    <col min="1" max="3" width="19.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1660,7 +1664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -1671,375 +1675,375 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="6">
-        <v>-3.134627745</v>
+        <v>-2.2946285739999999</v>
       </c>
       <c r="C4" s="7">
-        <v>-8.8844283669999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-8.9452178999999994</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="6">
-        <v>-8.2969333330000001</v>
+        <v>-5.7495708329999999</v>
       </c>
       <c r="C5" s="6">
-        <v>-19.512517620000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-19.547263749999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>1</v>
       </c>
       <c r="B6" s="6">
-        <v>-6.6978339240000002</v>
+        <v>-7.1317397000000005E-2</v>
       </c>
       <c r="C6" s="6">
-        <v>-6.6477093030000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-6.7054342739999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>2</v>
       </c>
       <c r="B7" s="6">
-        <v>-20.079526210000001</v>
+        <v>-19.698836140000001</v>
       </c>
       <c r="C7" s="6">
-        <v>-9.1898018480000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-9.287519219</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>3</v>
       </c>
       <c r="B8" s="6">
-        <v>-25.12024143</v>
+        <v>-26.461069389999999</v>
       </c>
       <c r="C8" s="6">
-        <v>-13.198829760000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-13.290643230000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>4</v>
       </c>
       <c r="B9" s="6">
-        <v>-29.36769408</v>
+        <v>-30.113616839999999</v>
       </c>
       <c r="C9" s="6">
-        <v>-17.264819159999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-17.35225642</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>5</v>
       </c>
       <c r="B10" s="6">
-        <v>-33.358860460000002</v>
+        <v>-33.795157619999998</v>
       </c>
       <c r="C10" s="6">
-        <v>-20.231054740000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-20.310462810000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>6</v>
       </c>
       <c r="B11" s="6">
-        <v>-37.754778389999998</v>
+        <v>-38.593029180000002</v>
       </c>
       <c r="C11" s="6">
-        <v>-22.611586800000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-22.693275400000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>7</v>
       </c>
       <c r="B12" s="6">
-        <v>-41.873334020000001</v>
+        <v>-42.763459320000003</v>
       </c>
       <c r="C12" s="6">
-        <v>-24.303556700000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-24.382036589999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>8</v>
       </c>
       <c r="B13" s="6">
-        <v>-45.608564309999998</v>
+        <v>-45.915071730000001</v>
       </c>
       <c r="C13" s="6">
-        <v>-25.5850501</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-25.643973679999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>9</v>
       </c>
       <c r="B14" s="6">
-        <v>-49.215965189999999</v>
+        <v>-48.749800209999997</v>
       </c>
       <c r="C14" s="6">
-        <v>-26.623976379999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-26.656041980000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>10</v>
       </c>
       <c r="B15" s="6">
-        <v>-52.039830119999998</v>
+        <v>-50.927608079999999</v>
       </c>
       <c r="C15" s="6">
-        <v>-27.534580980000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-27.540698630000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>11</v>
       </c>
       <c r="B16" s="6">
-        <v>-54.872374749999999</v>
+        <v>-53.388492530000001</v>
       </c>
       <c r="C16" s="6">
-        <v>-28.588661819999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-28.575592530000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>12</v>
       </c>
       <c r="B17" s="6">
-        <v>-58.332384300000001</v>
+        <v>-56.704416449999997</v>
       </c>
       <c r="C17" s="6">
-        <v>-29.896902310000002</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-29.87441793</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>13</v>
       </c>
       <c r="B18" s="6">
-        <v>-62.021799209999998</v>
+        <v>-60.284736819999999</v>
       </c>
       <c r="C18" s="6">
-        <v>-31.517388799999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-31.493182990000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>14</v>
       </c>
       <c r="B19" s="6">
-        <v>-65.753993679999994</v>
+        <v>-63.73719689</v>
       </c>
       <c r="C19" s="6">
-        <v>-33.330963150000002</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-33.310273520000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>15</v>
       </c>
       <c r="B20" s="6">
-        <v>-69.271178689999999</v>
+        <v>-66.889132689999997</v>
       </c>
       <c r="C20" s="6">
-        <v>-35.270356630000002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-35.255477339999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>16</v>
       </c>
       <c r="B21" s="6">
-        <v>-72.389395980000003</v>
+        <v>-69.683531700000003</v>
       </c>
       <c r="C21" s="6">
-        <v>-37.304146250000002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-37.295356040000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>17</v>
       </c>
       <c r="B22" s="6">
-        <v>-75.004637059999993</v>
+        <v>-72.018601439999998</v>
       </c>
       <c r="C22" s="6">
-        <v>-39.395071459999997</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-39.391869059999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>18</v>
       </c>
       <c r="B23" s="6">
-        <v>-77.091579780000004</v>
+        <v>-73.887692729999998</v>
       </c>
       <c r="C23" s="6">
-        <v>-41.480578600000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-41.483149300000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>19</v>
       </c>
       <c r="B24" s="6">
-        <v>-78.617889880000007</v>
+        <v>-75.336575179999997</v>
       </c>
       <c r="C24" s="6">
-        <v>-43.506062659999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-43.514330309999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>20</v>
       </c>
       <c r="B25" s="6">
-        <v>-79.676858940000002</v>
+        <v>-76.336133829999994</v>
       </c>
       <c r="C25" s="6">
-        <v>-45.407974009999997</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-45.422490160000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>21</v>
       </c>
       <c r="B26" s="6">
-        <v>-80.394952880000005</v>
+        <v>-77.119025969999996</v>
       </c>
       <c r="C26" s="6">
-        <v>-47.225787050000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-47.246572129999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>22</v>
       </c>
       <c r="B27" s="6">
-        <v>-80.985263750000001</v>
+        <v>-77.701040239999998</v>
       </c>
       <c r="C27" s="6">
-        <v>-48.97460959</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-49.001913780000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>23</v>
       </c>
       <c r="B28" s="6">
-        <v>-81.424163550000003</v>
+        <v>-78.269945379999996</v>
       </c>
       <c r="C28" s="6">
-        <v>-50.583230579999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-50.6161222</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>24</v>
       </c>
       <c r="B29" s="6">
-        <v>-81.838858110000004</v>
+        <v>-78.729215969999998</v>
       </c>
       <c r="C29" s="6">
-        <v>-51.987863869999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-52.02565139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>25</v>
       </c>
       <c r="B30" s="6">
-        <v>-82.241103469999999</v>
+        <v>-79.191535920000007</v>
       </c>
       <c r="C30" s="6">
-        <v>-53.129099150000002</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-53.170931439999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>26</v>
       </c>
       <c r="B31" s="6">
-        <v>-82.546846930000001</v>
+        <v>-79.690444580000005</v>
       </c>
       <c r="C31" s="6">
-        <v>-53.975407799999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-54.020373749999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>27</v>
       </c>
       <c r="B32" s="6">
-        <v>-82.865706590000002</v>
+        <v>-80.149463859999997</v>
       </c>
       <c r="C32" s="6">
-        <v>-54.546183999999997</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.592056280000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>28</v>
       </c>
       <c r="B33" s="6">
-        <v>-83.223837489999994</v>
+        <v>-80.703749779999995</v>
       </c>
       <c r="C33" s="6">
-        <v>-54.84183324</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.886465020000003</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>29</v>
       </c>
       <c r="B34" s="6">
-        <v>-83.649046080000005</v>
+        <v>-81.270359029999995</v>
       </c>
       <c r="C34" s="6">
-        <v>-54.862228979999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.902809339999997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>30</v>
       </c>
       <c r="B35" s="6">
-        <v>-84.139728160000004</v>
+        <v>-81.931367850000001</v>
       </c>
       <c r="C35" s="6">
-        <v>-54.644783750000002</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.678748370000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B36" s="8">
-        <v>-58.402805890375014</v>
+        <v>-56.504869504812497</v>
       </c>
       <c r="C36" s="8">
-        <v>-34.751782670562498</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-34.784768961343744</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>10</v>
       </c>
@@ -2057,22 +2061,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A65C64-A2BC-4A28-9AE0-4ADFC897F100}">
-  <sheetPr codeName="Sheet2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE138FB-FABF-4565-91D3-7A1FC3DB0D62}">
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="19.7109375" customWidth="1"/>
+    <col min="1" max="3" width="19.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2083,7 +2086,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -2094,375 +2097,375 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="6">
-        <v>5.0859756707999999</v>
+        <v>-3.134627745</v>
       </c>
       <c r="C4" s="7">
-        <v>-8.7527777610000008</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-8.8844283669999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="6">
-        <v>-3.2122312499999999</v>
+        <v>-8.2969333330000001</v>
       </c>
       <c r="C5" s="6">
-        <v>-19.551172210000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-19.512517620000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>1</v>
       </c>
       <c r="B6" s="6">
-        <v>-5.3938096389999997</v>
+        <v>-6.6978339240000002</v>
       </c>
       <c r="C6" s="6">
-        <v>-6.6258483119999996</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-6.6477093030000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>2</v>
       </c>
       <c r="B7" s="6">
-        <v>-17.6383081</v>
+        <v>-20.079526210000001</v>
       </c>
       <c r="C7" s="6">
-        <v>-9.1118174399999994</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-9.1898018480000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>3</v>
       </c>
       <c r="B8" s="6">
-        <v>-25.470428269999999</v>
+        <v>-25.12024143</v>
       </c>
       <c r="C8" s="6">
-        <v>-13.10593925</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-13.198829760000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>4</v>
       </c>
       <c r="B9" s="6">
-        <v>-28.583784139999999</v>
+        <v>-29.36769408</v>
       </c>
       <c r="C9" s="6">
-        <v>-17.15966766</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-17.264819159999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>5</v>
       </c>
       <c r="B10" s="6">
-        <v>-32.313720269999997</v>
+        <v>-33.358860460000002</v>
       </c>
       <c r="C10" s="6">
-        <v>-20.109887100000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-20.231054740000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>6</v>
       </c>
       <c r="B11" s="6">
-        <v>-38.931783619999997</v>
+        <v>-37.754778389999998</v>
       </c>
       <c r="C11" s="6">
-        <v>-22.460405290000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-22.611586800000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>7</v>
       </c>
       <c r="B12" s="6">
-        <v>-44.193969389999999</v>
+        <v>-41.873334020000001</v>
       </c>
       <c r="C12" s="6">
-        <v>-24.13231854</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-24.303556700000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>8</v>
       </c>
       <c r="B13" s="6">
-        <v>-47.542450969999997</v>
+        <v>-45.608564309999998</v>
       </c>
       <c r="C13" s="6">
-        <v>-25.411235569999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-25.5850501</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>9</v>
       </c>
       <c r="B14" s="6">
-        <v>-50.163651139999999</v>
+        <v>-49.215965189999999</v>
       </c>
       <c r="C14" s="6">
-        <v>-26.454934649999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-26.623976379999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>10</v>
       </c>
       <c r="B15" s="6">
-        <v>-52.336857309999999</v>
+        <v>-52.039830119999998</v>
       </c>
       <c r="C15" s="6">
-        <v>-27.373401099999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-27.534580980000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>11</v>
       </c>
       <c r="B16" s="6">
-        <v>-54.971295679999997</v>
+        <v>-54.872374749999999</v>
       </c>
       <c r="C16" s="6">
-        <v>-28.430558510000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-28.588661819999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>12</v>
       </c>
       <c r="B17" s="6">
-        <v>-58.43417676</v>
+        <v>-58.332384300000001</v>
       </c>
       <c r="C17" s="6">
-        <v>-29.734671070000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-29.896902310000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>13</v>
       </c>
       <c r="B18" s="6">
-        <v>-62.293765010000001</v>
+        <v>-62.021799209999998</v>
       </c>
       <c r="C18" s="6">
-        <v>-31.348709249999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-31.517388799999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>14</v>
       </c>
       <c r="B19" s="6">
-        <v>-66.011600229999999</v>
+        <v>-65.753993679999994</v>
       </c>
       <c r="C19" s="6">
-        <v>-33.155734270000004</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-33.330963150000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>15</v>
       </c>
       <c r="B20" s="6">
-        <v>-69.414165049999994</v>
+        <v>-69.271178689999999</v>
       </c>
       <c r="C20" s="6">
-        <v>-35.089932470000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-35.270356630000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>16</v>
       </c>
       <c r="B21" s="6">
-        <v>-72.491311699999997</v>
+        <v>-72.389395980000003</v>
       </c>
       <c r="C21" s="6">
-        <v>-37.12107932</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-37.304146250000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>17</v>
       </c>
       <c r="B22" s="6">
-        <v>-75.090810840000003</v>
+        <v>-75.004637059999993</v>
       </c>
       <c r="C22" s="6">
-        <v>-39.212890770000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-39.395071459999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>18</v>
       </c>
       <c r="B23" s="6">
-        <v>-77.190148410000006</v>
+        <v>-77.091579780000004</v>
       </c>
       <c r="C23" s="6">
-        <v>-41.302100979999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-41.480578600000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>19</v>
       </c>
       <c r="B24" s="6">
-        <v>-78.831857769999999</v>
+        <v>-78.617889880000007</v>
       </c>
       <c r="C24" s="6">
-        <v>-43.333805429999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-43.506062659999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>20</v>
       </c>
       <c r="B25" s="6">
-        <v>-79.984670260000001</v>
+        <v>-79.676858940000002</v>
       </c>
       <c r="C25" s="6">
-        <v>-45.243860439999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-45.407974009999997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>21</v>
       </c>
       <c r="B26" s="6">
-        <v>-80.892094299999997</v>
+        <v>-80.394952880000005</v>
       </c>
       <c r="C26" s="6">
-        <v>-47.07103085</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-47.225787050000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>22</v>
       </c>
       <c r="B27" s="6">
-        <v>-81.584893280000003</v>
+        <v>-80.985263750000001</v>
       </c>
       <c r="C27" s="6">
-        <v>-48.82968099</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-48.97460959</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>23</v>
       </c>
       <c r="B28" s="6">
-        <v>-82.188618529999999</v>
+        <v>-81.424163550000003</v>
       </c>
       <c r="C28" s="6">
-        <v>-50.447831409999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-50.583230579999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>24</v>
       </c>
       <c r="B29" s="6">
-        <v>-82.680878059999998</v>
+        <v>-81.838858110000004</v>
       </c>
       <c r="C29" s="6">
-        <v>-51.860813120000003</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-51.987863869999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>25</v>
       </c>
       <c r="B30" s="6">
-        <v>-83.151031070000002</v>
+        <v>-82.241103469999999</v>
       </c>
       <c r="C30" s="6">
-        <v>-53.008224439999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-53.129099150000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>26</v>
       </c>
       <c r="B31" s="6">
-        <v>-83.591067050000007</v>
+        <v>-82.546846930000001</v>
       </c>
       <c r="C31" s="6">
-        <v>-53.858057080000002</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-53.975407799999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>27</v>
       </c>
       <c r="B32" s="6">
-        <v>-84.032647600000004</v>
+        <v>-82.865706590000002</v>
       </c>
       <c r="C32" s="6">
-        <v>-54.429723799999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.546183999999997</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>28</v>
       </c>
       <c r="B33" s="6">
-        <v>-84.520683610000006</v>
+        <v>-83.223837489999994</v>
       </c>
       <c r="C33" s="6">
-        <v>-54.723002950000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.84183324</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>29</v>
       </c>
       <c r="B34" s="6">
-        <v>-85.024842120000002</v>
+        <v>-83.649046080000005</v>
       </c>
       <c r="C34" s="6">
-        <v>-54.737616420000002</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.862228979999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>30</v>
       </c>
       <c r="B35" s="6">
-        <v>-85.635214500000004</v>
+        <v>-84.139728160000004</v>
       </c>
       <c r="C35" s="6">
-        <v>-54.511005230000002</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.644783750000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B36" s="8">
-        <v>-58.397212195568756</v>
+        <v>-58.402805890375014</v>
       </c>
       <c r="C36" s="8">
-        <v>-34.615616677593756</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-34.751782670562498</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>10</v>
       </c>
@@ -2480,22 +2483,22 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36971AA9-8593-40CA-AF5E-AB605D9DEDA6}">
-  <sheetPr codeName="Sheet3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A65C64-A2BC-4A28-9AE0-4ADFC897F100}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="19.7109375" customWidth="1"/>
+    <col min="1" max="3" width="19.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2506,7 +2509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -2517,375 +2520,375 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="6">
-        <v>4.1547234381999996</v>
+        <v>5.0859756707999999</v>
       </c>
       <c r="C4" s="7">
-        <v>-8.7729818769999994</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-8.7527777610000008</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="6">
-        <v>-3.0644604169999998</v>
+        <v>-3.2122312499999999</v>
       </c>
       <c r="C5" s="6">
-        <v>-19.613466630000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-19.551172210000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>1</v>
       </c>
       <c r="B6" s="6">
-        <v>-8.3353299070000002</v>
+        <v>-5.3938096389999997</v>
       </c>
       <c r="C6" s="6">
-        <v>-6.5920257690000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-6.6258483119999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>2</v>
       </c>
       <c r="B7" s="6">
-        <v>-19.893430649999999</v>
+        <v>-17.6383081</v>
       </c>
       <c r="C7" s="6">
-        <v>-8.9759842499999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-9.1118174399999994</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>3</v>
       </c>
       <c r="B8" s="6">
-        <v>-24.992195519999999</v>
+        <v>-25.470428269999999</v>
       </c>
       <c r="C8" s="6">
-        <v>-12.948592189999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-13.10593925</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>4</v>
       </c>
       <c r="B9" s="6">
-        <v>-28.96165951</v>
+        <v>-28.583784139999999</v>
       </c>
       <c r="C9" s="6">
-        <v>-16.995025210000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-17.15966766</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>5</v>
       </c>
       <c r="B10" s="6">
-        <v>-33.009018849999997</v>
+        <v>-32.313720269999997</v>
       </c>
       <c r="C10" s="6">
-        <v>-19.939108900000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-20.109887100000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>6</v>
       </c>
       <c r="B11" s="6">
-        <v>-37.627369420000001</v>
+        <v>-38.931783619999997</v>
       </c>
       <c r="C11" s="6">
-        <v>-22.281845090000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-22.460405290000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>7</v>
       </c>
       <c r="B12" s="6">
-        <v>-41.938092330000003</v>
+        <v>-44.193969389999999</v>
       </c>
       <c r="C12" s="6">
-        <v>-23.96185191</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-24.13231854</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>8</v>
       </c>
       <c r="B13" s="6">
-        <v>-45.036503719999999</v>
+        <v>-47.542450969999997</v>
       </c>
       <c r="C13" s="6">
-        <v>-25.260750699999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-25.411235569999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>9</v>
       </c>
       <c r="B14" s="6">
-        <v>-47.993867690000002</v>
+        <v>-50.163651139999999</v>
       </c>
       <c r="C14" s="6">
-        <v>-26.324118139999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-26.454934649999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>10</v>
       </c>
       <c r="B15" s="6">
-        <v>-50.266548649999997</v>
+        <v>-52.336857309999999</v>
       </c>
       <c r="C15" s="6">
-        <v>-27.258422979999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-27.373401099999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>11</v>
       </c>
       <c r="B16" s="6">
-        <v>-52.839158380000001</v>
+        <v>-54.971295679999997</v>
       </c>
       <c r="C16" s="6">
-        <v>-28.321130780000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-28.430558510000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>12</v>
       </c>
       <c r="B17" s="6">
-        <v>-55.857302109999999</v>
+        <v>-58.43417676</v>
       </c>
       <c r="C17" s="6">
-        <v>-29.618544570000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-29.734671070000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>13</v>
       </c>
       <c r="B18" s="6">
-        <v>-59.28285846</v>
+        <v>-62.293765010000001</v>
       </c>
       <c r="C18" s="6">
-        <v>-31.21828373</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-31.348709249999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>14</v>
       </c>
       <c r="B19" s="6">
-        <v>-62.82900472</v>
+        <v>-66.011600229999999</v>
       </c>
       <c r="C19" s="6">
-        <v>-33.007581989999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-33.155734270000004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>15</v>
       </c>
       <c r="B20" s="6">
-        <v>-66.30202894</v>
+        <v>-69.414165049999994</v>
       </c>
       <c r="C20" s="6">
-        <v>-34.923720619999997</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-35.089932470000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>16</v>
       </c>
       <c r="B21" s="6">
-        <v>-69.429021000000006</v>
+        <v>-72.491311699999997</v>
       </c>
       <c r="C21" s="6">
-        <v>-36.938704399999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-37.12107932</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>17</v>
       </c>
       <c r="B22" s="6">
-        <v>-71.996276929999993</v>
+        <v>-75.090810840000003</v>
       </c>
       <c r="C22" s="6">
-        <v>-39.017543459999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-39.212890770000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>18</v>
       </c>
       <c r="B23" s="6">
-        <v>-74.120905410000006</v>
+        <v>-77.190148410000006</v>
       </c>
       <c r="C23" s="6">
-        <v>-41.096324389999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-41.302100979999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>19</v>
       </c>
       <c r="B24" s="6">
-        <v>-75.72266922</v>
+        <v>-78.831857769999999</v>
       </c>
       <c r="C24" s="6">
-        <v>-43.120406600000003</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-43.333805429999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>20</v>
       </c>
       <c r="B25" s="6">
-        <v>-76.814629780000004</v>
+        <v>-79.984670260000001</v>
       </c>
       <c r="C25" s="6">
-        <v>-45.024940800000003</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-45.243860439999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>21</v>
       </c>
       <c r="B26" s="6">
-        <v>-77.543292080000001</v>
+        <v>-80.892094299999997</v>
       </c>
       <c r="C26" s="6">
-        <v>-46.848219200000003</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-47.07103085</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>22</v>
       </c>
       <c r="B27" s="6">
-        <v>-78.176580079999994</v>
+        <v>-81.584893280000003</v>
       </c>
       <c r="C27" s="6">
-        <v>-48.604353869999997</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-48.82968099</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>23</v>
       </c>
       <c r="B28" s="6">
-        <v>-78.724552770000003</v>
+        <v>-82.188618529999999</v>
       </c>
       <c r="C28" s="6">
-        <v>-50.221350350000002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-50.447831409999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>24</v>
       </c>
       <c r="B29" s="6">
-        <v>-79.196423719999999</v>
+        <v>-82.680878059999998</v>
       </c>
       <c r="C29" s="6">
-        <v>-51.634098569999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-51.860813120000003</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>25</v>
       </c>
       <c r="B30" s="6">
-        <v>-79.598995669999994</v>
+        <v>-83.151031070000002</v>
       </c>
       <c r="C30" s="6">
-        <v>-52.781638620000003</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-53.008224439999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>26</v>
       </c>
       <c r="B31" s="6">
-        <v>-80.010856020000006</v>
+        <v>-83.591067050000007</v>
       </c>
       <c r="C31" s="6">
-        <v>-53.63195022</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-53.858057080000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>27</v>
       </c>
       <c r="B32" s="6">
-        <v>-80.42384946</v>
+        <v>-84.032647600000004</v>
       </c>
       <c r="C32" s="6">
-        <v>-54.205015520000003</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.429723799999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>28</v>
       </c>
       <c r="B33" s="6">
-        <v>-80.822470280000005</v>
+        <v>-84.520683610000006</v>
       </c>
       <c r="C33" s="6">
-        <v>-54.500440560000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.723002950000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>29</v>
       </c>
       <c r="B34" s="6">
-        <v>-81.315941719999998</v>
+        <v>-85.024842120000002</v>
       </c>
       <c r="C34" s="6">
-        <v>-54.517990879999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.737616420000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>30</v>
       </c>
       <c r="B35" s="6">
-        <v>-81.931346050000002</v>
+        <v>-85.635214500000004</v>
       </c>
       <c r="C35" s="6">
-        <v>-54.294941199999997</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.511005230000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B36" s="8">
-        <v>-56.246934875806247</v>
+        <v>-58.397212195568756</v>
       </c>
       <c r="C36" s="8">
-        <v>-34.451604811749995</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-34.615616677593756</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>10</v>
       </c>
@@ -2903,22 +2906,22 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F00F7CDB-E2F7-42FB-8E4C-712A9F309635}">
-  <sheetPr codeName="Sheet4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36971AA9-8593-40CA-AF5E-AB605D9DEDA6}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="19.5703125" customWidth="1"/>
+    <col min="1" max="3" width="19.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2929,7 +2932,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -2940,375 +2943,375 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="6">
-        <v>5.4069184514000002</v>
+        <v>4.1547234381999996</v>
       </c>
       <c r="C4" s="7">
-        <v>-8.9050473659999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-8.7729818769999994</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="6">
-        <v>2.37319375</v>
+        <v>-3.0644604169999998</v>
       </c>
       <c r="C5" s="6">
-        <v>-19.794978459999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-19.613466630000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>1</v>
       </c>
       <c r="B6" s="6">
-        <v>-2.35371679</v>
+        <v>-8.3353299070000002</v>
       </c>
       <c r="C6" s="6">
-        <v>-6.639183472</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-6.5920257690000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>2</v>
       </c>
       <c r="B7" s="6">
-        <v>-12.934701130000001</v>
+        <v>-19.893430649999999</v>
       </c>
       <c r="C7" s="6">
-        <v>-8.9260524790000009</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-8.9759842499999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>3</v>
       </c>
       <c r="B8" s="6">
-        <v>-19.97415548</v>
+        <v>-24.992195519999999</v>
       </c>
       <c r="C8" s="6">
-        <v>-12.832645080000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-12.948592189999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>4</v>
       </c>
       <c r="B9" s="6">
-        <v>-23.36141718</v>
+        <v>-28.96165951</v>
       </c>
       <c r="C9" s="6">
-        <v>-16.857665950000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-16.995025210000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>5</v>
       </c>
       <c r="B10" s="6">
-        <v>-26.713230490000001</v>
+        <v>-33.009018849999997</v>
       </c>
       <c r="C10" s="6">
-        <v>-19.796963720000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-19.939108900000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>6</v>
       </c>
       <c r="B11" s="6">
-        <v>-31.213914580000001</v>
+        <v>-37.627369420000001</v>
       </c>
       <c r="C11" s="6">
-        <v>-22.141197810000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-22.281845090000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>7</v>
       </c>
       <c r="B12" s="6">
-        <v>-35.071936430000001</v>
+        <v>-41.938092330000003</v>
       </c>
       <c r="C12" s="6">
-        <v>-23.833215809999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-23.96185191</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>8</v>
       </c>
       <c r="B13" s="6">
-        <v>-37.632387629999997</v>
+        <v>-45.036503719999999</v>
       </c>
       <c r="C13" s="6">
-        <v>-25.154644170000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-25.260750699999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>9</v>
       </c>
       <c r="B14" s="6">
-        <v>-39.872103250000002</v>
+        <v>-47.993867690000002</v>
       </c>
       <c r="C14" s="6">
-        <v>-26.238820130000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-26.324118139999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>10</v>
       </c>
       <c r="B15" s="6">
-        <v>-41.871231889999997</v>
+        <v>-50.266548649999997</v>
       </c>
       <c r="C15" s="6">
-        <v>-27.189217970000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-27.258422979999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>11</v>
       </c>
       <c r="B16" s="6">
-        <v>-44.309430540000001</v>
+        <v>-52.839158380000001</v>
       </c>
       <c r="C16" s="6">
-        <v>-28.257803729999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-28.321130780000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>12</v>
       </c>
       <c r="B17" s="6">
-        <v>-47.56648946</v>
+        <v>-55.857302109999999</v>
       </c>
       <c r="C17" s="6">
-        <v>-29.548414300000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-29.618544570000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>13</v>
       </c>
       <c r="B18" s="6">
-        <v>-51.069484750000001</v>
+        <v>-59.28285846</v>
       </c>
       <c r="C18" s="6">
-        <v>-31.132498510000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-31.21828373</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>14</v>
       </c>
       <c r="B19" s="6">
-        <v>-54.464428939999998</v>
+        <v>-62.82900472</v>
       </c>
       <c r="C19" s="6">
-        <v>-32.901003469999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-33.007581989999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>15</v>
       </c>
       <c r="B20" s="6">
-        <v>-57.549075340000002</v>
+        <v>-66.30202894</v>
       </c>
       <c r="C20" s="6">
-        <v>-34.795199869999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-34.923720619999997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>16</v>
       </c>
       <c r="B21" s="6">
-        <v>-60.243913120000002</v>
+        <v>-69.429021000000006</v>
       </c>
       <c r="C21" s="6">
-        <v>-36.78972907</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-36.938704399999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>17</v>
       </c>
       <c r="B22" s="6">
-        <v>-62.562240760000002</v>
+        <v>-71.996276929999993</v>
       </c>
       <c r="C22" s="6">
-        <v>-38.850998400000002</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-39.017543459999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>18</v>
       </c>
       <c r="B23" s="6">
-        <v>-64.466430939999995</v>
+        <v>-74.120905410000006</v>
       </c>
       <c r="C23" s="6">
-        <v>-40.914266439999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-41.096324389999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>19</v>
       </c>
       <c r="B24" s="6">
-        <v>-66.032298119999993</v>
+        <v>-75.72266922</v>
       </c>
       <c r="C24" s="6">
-        <v>-42.925040979999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-43.120406600000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>20</v>
       </c>
       <c r="B25" s="6">
-        <v>-67.192876929999997</v>
+        <v>-76.814629780000004</v>
       </c>
       <c r="C25" s="6">
-        <v>-44.818083479999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-45.024940800000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>21</v>
       </c>
       <c r="B26" s="6">
-        <v>-68.111643880000003</v>
+        <v>-77.543292080000001</v>
       </c>
       <c r="C26" s="6">
-        <v>-46.631318229999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-46.848219200000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>22</v>
       </c>
       <c r="B27" s="6">
-        <v>-68.932081030000006</v>
+        <v>-78.176580079999994</v>
       </c>
       <c r="C27" s="6">
-        <v>-48.378785520000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-48.604353869999997</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>23</v>
       </c>
       <c r="B28" s="6">
-        <v>-69.679363550000005</v>
+        <v>-78.724552770000003</v>
       </c>
       <c r="C28" s="6">
-        <v>-49.9887157</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-50.221350350000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>24</v>
       </c>
       <c r="B29" s="6">
-        <v>-70.388793120000003</v>
+        <v>-79.196423719999999</v>
       </c>
       <c r="C29" s="6">
-        <v>-51.396031000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-51.634098569999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>25</v>
       </c>
       <c r="B30" s="6">
-        <v>-71.113094469999993</v>
+        <v>-79.598995669999994</v>
       </c>
       <c r="C30" s="6">
-        <v>-52.539457319999997</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-52.781638620000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>26</v>
       </c>
       <c r="B31" s="6">
-        <v>-71.765117129999993</v>
+        <v>-80.010856020000006</v>
       </c>
       <c r="C31" s="6">
-        <v>-53.387141470000003</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-53.63195022</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>27</v>
       </c>
       <c r="B32" s="6">
-        <v>-72.390873580000004</v>
+        <v>-80.42384946</v>
       </c>
       <c r="C32" s="6">
-        <v>-53.959905630000002</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.205015520000003</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>28</v>
       </c>
       <c r="B33" s="6">
-        <v>-73.115541260000001</v>
+        <v>-80.822470280000005</v>
       </c>
       <c r="C33" s="6">
-        <v>-54.257519369999997</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.500440560000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>29</v>
       </c>
       <c r="B34" s="6">
-        <v>-73.885373290000004</v>
+        <v>-81.315941719999998</v>
       </c>
       <c r="C34" s="6">
-        <v>-54.279599709999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.517990879999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>30</v>
       </c>
       <c r="B35" s="6">
-        <v>-74.715274859999994</v>
+        <v>-81.931346050000002</v>
       </c>
       <c r="C35" s="6">
-        <v>-54.063435810000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.294941199999997</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B36" s="8">
-        <v>-48.524140866206253</v>
+        <v>-56.246934875806247</v>
       </c>
       <c r="C36" s="8">
-        <v>-34.316393138343749</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-34.451604811749995</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>10</v>
       </c>
@@ -3326,22 +3329,22 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A43502-C709-47ED-82F5-620B67AC7AF2}">
-  <sheetPr codeName="Sheet5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F00F7CDB-E2F7-42FB-8E4C-712A9F309635}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="19.5703125" customWidth="1"/>
+    <col min="1" max="3" width="19.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -3352,7 +3355,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -3363,375 +3366,375 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="6">
-        <v>8.3710618562000008</v>
+        <v>5.4069184514000002</v>
       </c>
       <c r="C4" s="7">
-        <v>-9.1223835040000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-8.9050473659999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="6">
-        <v>6.8827604167000001</v>
+        <v>2.37319375</v>
       </c>
       <c r="C5" s="6">
-        <v>-20.07372711</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-19.794978459999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>1</v>
       </c>
       <c r="B6" s="6">
-        <v>-0.45804236300000001</v>
+        <v>-2.35371679</v>
       </c>
       <c r="C6" s="6">
-        <v>-6.7572968769999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-6.639183472</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>2</v>
       </c>
       <c r="B7" s="6">
-        <v>-12.71941795</v>
+        <v>-12.934701130000001</v>
       </c>
       <c r="C7" s="6">
-        <v>-8.8279884079999995</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-8.9260524790000009</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>3</v>
       </c>
       <c r="B8" s="6">
-        <v>-20.15243714</v>
+        <v>-19.97415548</v>
       </c>
       <c r="C8" s="6">
-        <v>-12.588669919999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-12.832645080000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>4</v>
       </c>
       <c r="B9" s="6">
-        <v>-23.751924819999999</v>
+        <v>-23.36141718</v>
       </c>
       <c r="C9" s="6">
-        <v>-16.554409629999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-16.857665950000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>5</v>
       </c>
       <c r="B10" s="6">
-        <v>-27.194243180000001</v>
+        <v>-26.713230490000001</v>
       </c>
       <c r="C10" s="6">
-        <v>-19.512283499999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-19.796963720000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>6</v>
       </c>
       <c r="B11" s="6">
-        <v>-32.489066280000003</v>
+        <v>-31.213914580000001</v>
       </c>
       <c r="C11" s="6">
-        <v>-21.90164253</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-22.141197810000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>7</v>
       </c>
       <c r="B12" s="6">
-        <v>-36.337831289999997</v>
+        <v>-35.071936430000001</v>
       </c>
       <c r="C12" s="6">
-        <v>-23.653459680000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-23.833215809999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>8</v>
       </c>
       <c r="B13" s="6">
-        <v>-38.706014519999997</v>
+        <v>-37.632387629999997</v>
       </c>
       <c r="C13" s="6">
-        <v>-25.049233730000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-25.154644170000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>9</v>
       </c>
       <c r="B14" s="6">
-        <v>-40.471754949999998</v>
+        <v>-39.872103250000002</v>
       </c>
       <c r="C14" s="6">
-        <v>-26.202677690000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-26.238820130000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>10</v>
       </c>
       <c r="B15" s="6">
-        <v>-42.00349147</v>
+        <v>-41.871231889999997</v>
       </c>
       <c r="C15" s="6">
-        <v>-27.206369429999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-27.189217970000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>11</v>
       </c>
       <c r="B16" s="6">
-        <v>-44.176867280000003</v>
+        <v>-44.309430540000001</v>
       </c>
       <c r="C16" s="6">
-        <v>-28.301749300000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-28.257803729999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>12</v>
       </c>
       <c r="B17" s="6">
-        <v>-46.912354790000002</v>
+        <v>-47.56648946</v>
       </c>
       <c r="C17" s="6">
-        <v>-29.595148940000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-29.548414300000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>13</v>
       </c>
       <c r="B18" s="6">
-        <v>-49.899324960000001</v>
+        <v>-51.069484750000001</v>
       </c>
       <c r="C18" s="6">
-        <v>-31.164094469999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-31.132498510000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>14</v>
       </c>
       <c r="B19" s="6">
-        <v>-52.964594329999997</v>
+        <v>-54.464428939999998</v>
       </c>
       <c r="C19" s="6">
-        <v>-32.906071109999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-32.901003469999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>15</v>
       </c>
       <c r="B20" s="6">
-        <v>-55.842553180000003</v>
+        <v>-57.549075340000002</v>
       </c>
       <c r="C20" s="6">
-        <v>-34.769279509999997</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-34.795199869999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>16</v>
       </c>
       <c r="B21" s="6">
-        <v>-58.401681119999999</v>
+        <v>-60.243913120000002</v>
       </c>
       <c r="C21" s="6">
-        <v>-36.734082770000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-36.78972907</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>17</v>
       </c>
       <c r="B22" s="6">
-        <v>-60.589063639999999</v>
+        <v>-62.562240760000002</v>
       </c>
       <c r="C22" s="6">
-        <v>-38.767443</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-38.850998400000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>18</v>
       </c>
       <c r="B23" s="6">
-        <v>-62.395214369999998</v>
+        <v>-64.466430939999995</v>
       </c>
       <c r="C23" s="6">
-        <v>-40.803412960000003</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-40.914266439999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>19</v>
       </c>
       <c r="B24" s="6">
-        <v>-63.906038039999999</v>
+        <v>-66.032298119999993</v>
       </c>
       <c r="C24" s="6">
-        <v>-42.78701478</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-42.925040979999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>20</v>
       </c>
       <c r="B25" s="6">
-        <v>-65.080182550000004</v>
+        <v>-67.192876929999997</v>
       </c>
       <c r="C25" s="6">
-        <v>-44.652505580000003</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-44.818083479999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>21</v>
       </c>
       <c r="B26" s="6">
-        <v>-66.067297150000002</v>
+        <v>-68.111643880000003</v>
       </c>
       <c r="C26" s="6">
-        <v>-46.43781911</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-46.631318229999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>22</v>
       </c>
       <c r="B27" s="6">
-        <v>-67.064761509999997</v>
+        <v>-68.932081030000006</v>
       </c>
       <c r="C27" s="6">
-        <v>-48.159291840000002</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-48.378785520000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>23</v>
       </c>
       <c r="B28" s="6">
-        <v>-68.000502510000004</v>
+        <v>-69.679363550000005</v>
       </c>
       <c r="C28" s="6">
-        <v>-49.745504920000002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-49.9887157</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>24</v>
       </c>
       <c r="B29" s="6">
-        <v>-68.888497229999999</v>
+        <v>-70.388793120000003</v>
       </c>
       <c r="C29" s="6">
-        <v>-51.13243095</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-51.396031000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>25</v>
       </c>
       <c r="B30" s="6">
-        <v>-69.799231989999996</v>
+        <v>-71.113094469999993</v>
       </c>
       <c r="C30" s="6">
-        <v>-52.258362290000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-52.539457319999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>26</v>
       </c>
       <c r="B31" s="6">
-        <v>-70.670586290000003</v>
+        <v>-71.765117129999993</v>
       </c>
       <c r="C31" s="6">
-        <v>-53.092458290000003</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-53.387141470000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>27</v>
       </c>
       <c r="B32" s="6">
-        <v>-71.565499059999993</v>
+        <v>-72.390873580000004</v>
       </c>
       <c r="C32" s="6">
-        <v>-53.656817369999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-53.959905630000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>28</v>
       </c>
       <c r="B33" s="6">
-        <v>-72.464189930000003</v>
+        <v>-73.115541260000001</v>
       </c>
       <c r="C33" s="6">
-        <v>-53.951834089999998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.257519369999997</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>29</v>
       </c>
       <c r="B34" s="6">
-        <v>-73.397111649999999</v>
+        <v>-73.885373290000004</v>
       </c>
       <c r="C34" s="6">
-        <v>-53.977415229999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.279599709999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>30</v>
       </c>
       <c r="B35" s="6">
-        <v>-74.446040249999996</v>
+        <v>-74.715274859999994</v>
       </c>
       <c r="C35" s="6">
-        <v>-53.770619439999997</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-54.063435810000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B36" s="8">
-        <v>-47.548812297503126</v>
+        <v>-48.524140866206253</v>
       </c>
       <c r="C36" s="8">
-        <v>-34.191046811218747</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-34.316393138343749</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>10</v>
       </c>
@@ -3749,22 +3752,22 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0334E61F-4137-42F1-8ADC-1EC55566A90B}">
-  <sheetPr codeName="Sheet1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A43502-C709-47ED-82F5-620B67AC7AF2}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="19.7109375" customWidth="1"/>
+    <col min="1" max="3" width="19.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -3775,7 +3778,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -3786,375 +3789,375 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="6">
-        <v>7.8807580462000004</v>
+        <v>8.3710618562000008</v>
       </c>
       <c r="C4" s="7">
-        <v>-9.1849778220000005</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-9.1223835040000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="6">
-        <v>3.0264520833000002</v>
+        <v>6.8827604167000001</v>
       </c>
       <c r="C5" s="6">
-        <v>-20.17021621</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-20.07372711</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>1</v>
       </c>
       <c r="B6" s="6">
-        <v>2.7109457350000001</v>
+        <v>-0.45804236300000001</v>
       </c>
       <c r="C6" s="6">
-        <v>-6.7807565470000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-6.7572968769999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>2</v>
       </c>
       <c r="B7" s="6">
-        <v>-12.88959281</v>
+        <v>-12.71941795</v>
       </c>
       <c r="C7" s="6">
-        <v>-8.7977132959999995</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-8.8279884079999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>3</v>
       </c>
       <c r="B8" s="6">
-        <v>-19.98805325</v>
+        <v>-20.15243714</v>
       </c>
       <c r="C8" s="6">
-        <v>-12.5498672</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-12.588669919999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>4</v>
       </c>
       <c r="B9" s="6">
-        <v>-24.302522759999999</v>
+        <v>-23.751924819999999</v>
       </c>
       <c r="C9" s="6">
-        <v>-16.51681786</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-16.554409629999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>5</v>
       </c>
       <c r="B10" s="6">
-        <v>-28.36529337</v>
+        <v>-27.194243180000001</v>
       </c>
       <c r="C10" s="6">
-        <v>-19.471623770000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-19.512283499999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>6</v>
       </c>
       <c r="B11" s="6">
-        <v>-33.281085609999998</v>
+        <v>-32.489066280000003</v>
       </c>
       <c r="C11" s="6">
-        <v>-21.85039106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-21.90164253</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>7</v>
       </c>
       <c r="B12" s="6">
-        <v>-37.424965550000003</v>
+        <v>-36.337831289999997</v>
       </c>
       <c r="C12" s="6">
-        <v>-23.59367825</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-23.653459680000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>8</v>
       </c>
       <c r="B13" s="6">
-        <v>-40.527535700000001</v>
+        <v>-38.706014519999997</v>
       </c>
       <c r="C13" s="6">
-        <v>-24.986055270000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-25.049233730000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>9</v>
       </c>
       <c r="B14" s="6">
-        <v>-43.148749610000003</v>
+        <v>-40.471754949999998</v>
       </c>
       <c r="C14" s="6">
-        <v>-26.13804378</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-26.202677690000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>10</v>
       </c>
       <c r="B15" s="6">
-        <v>-45.445842380000002</v>
+        <v>-42.00349147</v>
       </c>
       <c r="C15" s="6">
-        <v>-27.14059645</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-27.206369429999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>11</v>
       </c>
       <c r="B16" s="6">
-        <v>-47.954319310000002</v>
+        <v>-44.176867280000003</v>
       </c>
       <c r="C16" s="6">
-        <v>-28.23302752</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-28.301749300000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>12</v>
       </c>
       <c r="B17" s="6">
-        <v>-50.895752739999999</v>
+        <v>-46.912354790000002</v>
       </c>
       <c r="C17" s="6">
-        <v>-29.521375190000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-29.595148940000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>13</v>
       </c>
       <c r="B18" s="6">
-        <v>-53.965127780000003</v>
+        <v>-49.899324960000001</v>
       </c>
       <c r="C18" s="6">
-        <v>-31.084980699999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-31.164094469999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>14</v>
       </c>
       <c r="B19" s="6">
-        <v>-56.996038859999999</v>
+        <v>-52.964594329999997</v>
       </c>
       <c r="C19" s="6">
-        <v>-32.822222109999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-32.906071109999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>15</v>
       </c>
       <c r="B20" s="6">
-        <v>-59.980257080000001</v>
+        <v>-55.842553180000003</v>
       </c>
       <c r="C20" s="6">
-        <v>-34.681412080000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-34.769279509999997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>16</v>
       </c>
       <c r="B21" s="6">
-        <v>-62.745383459999999</v>
+        <v>-58.401681119999999</v>
       </c>
       <c r="C21" s="6">
-        <v>-36.643586249999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-36.734082770000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>17</v>
       </c>
       <c r="B22" s="6">
-        <v>-65.175414779999997</v>
+        <v>-60.589063639999999</v>
       </c>
       <c r="C22" s="6">
-        <v>-38.67573719</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-38.767443</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>18</v>
       </c>
       <c r="B23" s="6">
-        <v>-67.270893119999997</v>
+        <v>-62.395214369999998</v>
       </c>
       <c r="C23" s="6">
-        <v>-40.711742039999997</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-40.803412960000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>19</v>
       </c>
       <c r="B24" s="6">
-        <v>-69.03882935</v>
+        <v>-63.906038039999999</v>
       </c>
       <c r="C24" s="6">
-        <v>-42.696366140000002</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-42.78701478</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>20</v>
       </c>
       <c r="B25" s="6">
-        <v>-70.43978491</v>
+        <v>-65.080182550000004</v>
       </c>
       <c r="C25" s="6">
-        <v>-44.563470369999997</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-44.652505580000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>21</v>
       </c>
       <c r="B26" s="6">
-        <v>-71.633975890000002</v>
+        <v>-66.067297150000002</v>
       </c>
       <c r="C26" s="6">
-        <v>-46.350588930000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-46.43781911</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>22</v>
       </c>
       <c r="B27" s="6">
-        <v>-72.828563149999994</v>
+        <v>-67.064761509999997</v>
       </c>
       <c r="C27" s="6">
-        <v>-48.073858280000003</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-48.159291840000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>23</v>
       </c>
       <c r="B28" s="6">
-        <v>-73.914798529999999</v>
+        <v>-68.000502510000004</v>
       </c>
       <c r="C28" s="6">
-        <v>-49.661632480000002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-49.745504920000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>24</v>
       </c>
       <c r="B29" s="6">
-        <v>-74.985240709999999</v>
+        <v>-68.888497229999999</v>
       </c>
       <c r="C29" s="6">
-        <v>-51.049575089999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-51.13243095</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>25</v>
       </c>
       <c r="B30" s="6">
-        <v>-75.972331120000007</v>
+        <v>-69.799231989999996</v>
       </c>
       <c r="C30" s="6">
-        <v>-52.175731300000002</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-52.258362290000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>26</v>
       </c>
       <c r="B31" s="6">
-        <v>-76.947613270000005</v>
+        <v>-70.670586290000003</v>
       </c>
       <c r="C31" s="6">
-        <v>-53.00927935</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-53.092458290000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>27</v>
       </c>
       <c r="B32" s="6">
-        <v>-77.947125740000004</v>
+        <v>-71.565499059999993</v>
       </c>
       <c r="C32" s="6">
-        <v>-53.57238194</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-53.656817369999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>28</v>
       </c>
       <c r="B33" s="6">
-        <v>-78.902608549999997</v>
+        <v>-72.464189930000003</v>
       </c>
       <c r="C33" s="6">
-        <v>-53.865276379999997</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-53.951834089999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>29</v>
       </c>
       <c r="B34" s="6">
-        <v>-79.884070080000001</v>
+        <v>-73.397111649999999</v>
       </c>
       <c r="C34" s="6">
-        <v>-53.887956340000002</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-53.977415229999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>30</v>
       </c>
       <c r="B35" s="6">
-        <v>-80.923544419999999</v>
+        <v>-74.446040249999996</v>
       </c>
       <c r="C35" s="6">
-        <v>-53.677299189999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-53.770619439999997</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B36" s="8">
-        <v>-51.254911188296873</v>
+        <v>-47.548812297503126</v>
       </c>
       <c r="C36" s="8">
-        <v>-34.129319887031251</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-34.191046811218747</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>10</v>
       </c>
@@ -4172,27 +4175,450 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0334E61F-4137-42F1-8ADC-1EC55566A90B}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:E39"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="3" width="19.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="6">
+        <v>7.8807580462000004</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-9.1849778220000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="6">
+        <v>3.0264520833000002</v>
+      </c>
+      <c r="C5" s="6">
+        <v>-20.17021621</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6">
+        <v>2.7109457350000001</v>
+      </c>
+      <c r="C6" s="6">
+        <v>-6.7807565470000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="5">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6">
+        <v>-12.88959281</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-8.7977132959999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6">
+        <v>-19.98805325</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-12.5498672</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="5">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6">
+        <v>-24.302522759999999</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-16.51681786</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="5">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6">
+        <v>-28.36529337</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-19.471623770000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="5">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6">
+        <v>-33.281085609999998</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-21.85039106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6">
+        <v>-37.424965550000003</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-23.59367825</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="5">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6">
+        <v>-40.527535700000001</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-24.986055270000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="5">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6">
+        <v>-43.148749610000003</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-26.13804378</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="5">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6">
+        <v>-45.445842380000002</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-27.14059645</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="5">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6">
+        <v>-47.954319310000002</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-28.23302752</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="5">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6">
+        <v>-50.895752739999999</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-29.521375190000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="5">
+        <v>13</v>
+      </c>
+      <c r="B18" s="6">
+        <v>-53.965127780000003</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-31.084980699999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="5">
+        <v>14</v>
+      </c>
+      <c r="B19" s="6">
+        <v>-56.996038859999999</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-32.822222109999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="5">
+        <v>15</v>
+      </c>
+      <c r="B20" s="6">
+        <v>-59.980257080000001</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-34.681412080000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <v>16</v>
+      </c>
+      <c r="B21" s="6">
+        <v>-62.745383459999999</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-36.643586249999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="5">
+        <v>17</v>
+      </c>
+      <c r="B22" s="6">
+        <v>-65.175414779999997</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-38.67573719</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="5">
+        <v>18</v>
+      </c>
+      <c r="B23" s="6">
+        <v>-67.270893119999997</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-40.711742039999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="5">
+        <v>19</v>
+      </c>
+      <c r="B24" s="6">
+        <v>-69.03882935</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-42.696366140000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="5">
+        <v>20</v>
+      </c>
+      <c r="B25" s="6">
+        <v>-70.43978491</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-44.563470369999997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="5">
+        <v>21</v>
+      </c>
+      <c r="B26" s="6">
+        <v>-71.633975890000002</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-46.350588930000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="5">
+        <v>22</v>
+      </c>
+      <c r="B27" s="6">
+        <v>-72.828563149999994</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-48.073858280000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="5">
+        <v>23</v>
+      </c>
+      <c r="B28" s="6">
+        <v>-73.914798529999999</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-49.661632480000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="5">
+        <v>24</v>
+      </c>
+      <c r="B29" s="6">
+        <v>-74.985240709999999</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-51.049575089999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="5">
+        <v>25</v>
+      </c>
+      <c r="B30" s="6">
+        <v>-75.972331120000007</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-52.175731300000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="5">
+        <v>26</v>
+      </c>
+      <c r="B31" s="6">
+        <v>-76.947613270000005</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-53.00927935</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="5">
+        <v>27</v>
+      </c>
+      <c r="B32" s="6">
+        <v>-77.947125740000004</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-53.57238194</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" s="5">
+        <v>28</v>
+      </c>
+      <c r="B33" s="6">
+        <v>-78.902608549999997</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-53.865276379999997</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" s="5">
+        <v>29</v>
+      </c>
+      <c r="B34" s="6">
+        <v>-79.884070080000001</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-53.887956340000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" s="5">
+        <v>30</v>
+      </c>
+      <c r="B35" s="6">
+        <v>-80.923544419999999</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-53.677299189999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="8">
+        <v>-51.254911188296873</v>
+      </c>
+      <c r="C36" s="8">
+        <v>-34.129319887031251</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A39:E39"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25262A5-84B2-4BF6-AF4E-DBAA1AC8379B}">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="H31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="31" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H31" s="1"/>
     </row>
   </sheetData>
